--- a/MO001.xlsx
+++ b/MO001.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D0598B-D442-42A2-AA42-BB06A2B50749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBA9A20-1598-4290-9486-B4982EAF767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Story ID</t>
   </si>
@@ -71,23 +71,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>As a MO, I want to publish TA recruitment jobs with detailed information, so that eligible TA applicants can browse and apply for the relevant jobs.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>View Applicant List for Published Jobs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>As a MO, I want to view a complete list of applicants for the jobs I published, so that I can quickly get an overview of all applicants for my jobs.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Filter and Mark Applicant Status</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As a MO, I want to mark applicants' status as "Approved"/"Rejected"/"Pending Interview" for the jobs I published, so that I can manage the recruitment review process and notify applicants of the results.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -95,21 +83,6 @@
 2. After marking as "Approved"/"Rejected", the system automatically generates a status notification and saves it to the applicant's notification file;
 3. Marking records are automatically saved with Marked By, Mark Time and Status for traceability;
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. After logging in, MO can only view applicants for their own published jobs, not for other MOs' jobs;
-2. The list displays the following fields: Applicant ID, Name, Application Time, Core Skill Tags, Application Status;
-3. Clicking the applicant's name jumps to the CV detail page;
-4. The list supports filtering by application status (Pending Review/Approved/Rejected).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Edit and Delete Published Jobs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>As a MO, I want to edit the details of my published jobs and take down jobs that are no longer recruiting, so that I can update job information and stop invalid applications.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -121,78 +94,71 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">	AI-assisted Screening of High-matching-rate Applicants</t>
+    <t>MO001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>As a MO, I want the system to AI-identify and highlight the high-matching-rate applicants for my jobs, so that I can focus on reviewing the most qualified applicants.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. AI automatically screens out high-matching-rate applicants for the job based on the matching rate and displays them in a separate section;
-2. The high-matching-rate threshold (30%) can be manually adjusted by MO;
-3. Highlight display includes Matching Rate, Core Matched Skills and Recommendation Reasons;
-4. AI recommendation results can be refreshed and support excluding specified applicants;
-5. Recommendation results do not affect MO's manual screening and are only for auxiliary reference.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>M</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>L</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Applicant skill tags extract core keywords from TA resumes;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Status marking data is stored in JSON format and associated with Job ID-Applicant ID;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1. MO can fill in core job information (job title, skill requirements, weekly workload, application deadline);
+    <t>MO002</t>
+  </si>
+  <si>
+    <t>MO003</t>
+  </si>
+  <si>
+    <t>MO004</t>
+  </si>
+  <si>
+    <t>As a MO, I want to publish TA recruitment jobs with detailed information, so that eligible TA applicants can browse and apply for the relevant jobs.</t>
+  </si>
+  <si>
+    <t>Must have</t>
+  </si>
+  <si>
+    <t>1. MO can fill in core job information (job title, skill requirements, weekly workload, application deadline);
 2. Published jobs are automatically displayed in the "Available Jobs" section of the system;
 3. Job information is automatically saved as a JSON file after submission;
 4. Only the publishing MO can edit their own jobs, and administrators can view all MO-published jobs.
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+5.MO can restrict only TA with specific conditions to apply at the time of release</t>
+  </si>
+  <si>
+    <t>3 story points</t>
   </si>
   <si>
     <t>Naming rule for storage files: MO_JobID_PublishDate.json;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. After logging in, MO can only view applicants for their own published jobs, not for other MOs' jobs;
+2. The list displays the following fields: Applicant ID, Name, Application Time, Application Status;
+3. Clicking the applicant's name jumps to the CV detail page;
+4. The list supports filtering by application status (Pending Review/Approved/Rejected).</t>
+  </si>
+  <si>
+    <t>2 story points</t>
+  </si>
+  <si>
+    <t>Applicant skill tags extract core keywords from TA resumes;</t>
+  </si>
+  <si>
+    <t>Filter and Mark Applicant Status</t>
+  </si>
+  <si>
+    <t>As a MO, I want to mark applicants' status as "Approved"/"Rejected"/"Pending Interview" for the jobs I published, so that I can manage the recruitment review process and notify applicants of the results.</t>
+  </si>
+  <si>
+    <t>Status marking data is stored in JSON format and associated with Job ID-Applicant ID;</t>
+  </si>
+  <si>
+    <t>Edit and Delete Published Jobs</t>
+  </si>
+  <si>
+    <t>As a MO, I want to edit the details of my published jobs and take down jobs that are no longer recruiting, so that I can update job information and stop invalid applications.</t>
+  </si>
+  <si>
+    <t>Should have</t>
   </si>
   <si>
     <t>1. Edit operations only modify the original job CSV file without generating new files;
 2. Take-down status is stored in the JSON configuration file of job information;
 3. Deadline automatic validation is triggered regularly by the system.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommendation reasons are automatically generated by AI </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MO001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MO002</t>
-  </si>
-  <si>
-    <t>MO003</t>
-  </si>
-  <si>
-    <t>MO004</t>
-  </si>
-  <si>
-    <t>MO005</t>
   </si>
 </sst>
 </file>
@@ -200,7 +166,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="184" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -300,7 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -699,30 +665,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="189" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" ht="216" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="1">
-        <v>3</v>
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4">
         <v>46101</v>
@@ -733,131 +699,103 @@
     </row>
     <row r="4" spans="1:10" ht="175.5" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I4" s="4">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="J4" s="4">
-        <v>46112</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="175.5" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="4">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="J5" s="4">
-        <v>46112</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="256.5" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I6" s="4">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="J6" s="4">
-        <v>46117</v>
+        <v>46112</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="229.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="4">
-        <v>46117</v>
-      </c>
-      <c r="J7" s="4">
-        <v>46123</v>
-      </c>
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.15">
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
